--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.15-16-18-identity-access-management/WKBK/90_workbooks/ISMS-IMP-A.5.15-16-18.S4_Role_Compliance_SoD_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.15-16-18-identity-access-management/WKBK/90_workbooks/ISMS-IMP-A.5.15-16-18.S4_Role_Compliance_SoD_20260208.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08.02.2026 11:48</t>
+          <t>08.02.2026 12:25</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>05.11.2025</t>
+          <t>04.01.2026</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>04.08.2025</t>
+          <t>23.07.2025</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>14.08.2025</t>
+          <t>17.10.2025</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>31.08.2025</t>
+          <t>19.04.2025</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>02.11.2025</t>
+          <t>20.11.2025</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>08.03.2025</t>
+          <t>17.08.2025</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>02.01.2026</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>16.05.2025</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>11.04.2025</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>28.04.2025</t>
+          <t>07.07.2025</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>02.05.2025</t>
+          <t>04.08.2025</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>07.12.2025</t>
+          <t>21.12.2025</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>07.08.2025</t>
+          <t>20.03.2025</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>29.05.2025</t>
+          <t>12.07.2025</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>22.11.2025</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>19.06.2025</t>
+          <t>24.05.2025</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>29.12.2025</t>
+          <t>23.03.2025</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>20.10.2025</t>
+          <t>16.02.2025</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>15.12.2025</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>02.04.2025</t>
+          <t>28.02.2025</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>13.09.2025</t>
+          <t>22.12.2025</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>13.04.2025</t>
+          <t>04.04.2025</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>12.05.2025</t>
+          <t>19.12.2025</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>12.04.2025</t>
+          <t>02.06.2025</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>14.02.2025</t>
+          <t>03.11.2025</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>15.06.2025</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>28.12.2025</t>
+          <t>01.08.2025</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>08.08.2025</t>
+          <t>31.03.2025</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>29.07.2025</t>
+          <t>23.08.2025</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>13.08.2025</t>
+          <t>06.08.2025</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
@@ -2767,32 +2767,32 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>kate.garcia</t>
+          <t>iris.miller</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Kate Garcia</t>
+          <t>Iris Miller</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>IT Administrator</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>25.11.2025</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
@@ -2819,32 +2819,32 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>david.brown</t>
+          <t>grace.brown</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>David Brown</t>
+          <t>Grace Brown</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Sales Operations</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>14.11.2024</t>
+          <t>11.09.2024</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
@@ -2871,32 +2871,32 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>nathan.jones</t>
+          <t>iris.johnson</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Nathan Jones</t>
+          <t>Iris Johnson</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>04.08.2024</t>
+          <t>19.12.2025</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
@@ -2923,32 +2923,32 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>jack.johnson</t>
+          <t>alice.smith</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Jack Johnson</t>
+          <t>Alice Smith</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>22.11.2024</t>
+          <t>25.11.2025</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
@@ -2975,32 +2975,32 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>mary.garcia</t>
+          <t>alice.miller</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Mary Garcia</t>
+          <t>Alice Miller</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>24.12.2024</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="J10" s="9" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>alice.brown</t>
+          <t>bob.smith</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Alice Brown</t>
+          <t>Bob Smith</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -3042,17 +3042,17 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>30.09.2024</t>
+          <t>24.08.2025</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -3079,32 +3079,32 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>jack.brown</t>
+          <t>alice.davis</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Jack Brown</t>
+          <t>Alice Davis</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Recruiter</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>15.12.2024</t>
+          <t>22.02.2024</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>bob.brown</t>
+          <t>bob.williams</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Bob Brown</t>
+          <t>Bob Williams</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>30.01.2025</t>
+          <t>08.10.2025</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -3159,9 +3159,9 @@
           <t>Inherited</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
@@ -3183,32 +3183,32 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>bob.jones</t>
+          <t>frank.smith</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Bob Jones</t>
+          <t>Frank Smith</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>30.10.2024</t>
+          <t>16.07.2024</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
@@ -3235,17 +3235,17 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>iris.smith</t>
+          <t>iris.brown</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Iris Smith</t>
+          <t>Iris Brown</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>22.11.2025</t>
+          <t>15.12.2025</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
@@ -3287,27 +3287,27 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>grace.jones</t>
+          <t>grace.johnson</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Grace Jones</t>
+          <t>Grace Johnson</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>07.07.2024</t>
+          <t>13.08.2024</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
@@ -3339,42 +3339,42 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>henry.johnson</t>
+          <t>bob.williams</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Henry Johnson</t>
+          <t>Bob Williams</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>07.09.2024</t>
+          <t>17.10.2025</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Automatic</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>Needs Review</t>
+          <t>Inherited</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
@@ -3391,27 +3391,27 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>liam.davis</t>
+          <t>iris.miller</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Liam Davis</t>
+          <t>Iris Miller</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sales Operations</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>20.11.2024</t>
+          <t>17.07.2024</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
@@ -3443,17 +3443,17 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>kate.jones</t>
+          <t>peter.davis</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Kate Jones</t>
+          <t>Peter Davis</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>01.12.2024</t>
+          <t>22.12.2024</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>grace.davis</t>
+          <t>grace.garcia</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Grace Davis</t>
+          <t>Grace Garcia</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -3510,17 +3510,17 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>17.08.2025</t>
+          <t>13.08.2024</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
@@ -3547,32 +3547,32 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>mary.johnson</t>
+          <t>frank.garcia</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Mary Johnson</t>
+          <t>Frank Garcia</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>19.07.2024</t>
+          <t>11.04.2024</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
@@ -3599,27 +3599,27 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>kate.jones</t>
+          <t>grace.johnson</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Kate Jones</t>
+          <t>Grace Johnson</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>20.09.2025</t>
+          <t>09.09.2024</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
@@ -3651,32 +3651,32 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>grace.davis</t>
+          <t>david.garcia</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Grace Davis</t>
+          <t>David Garcia</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>HR Generalist</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>24.09.2024</t>
+          <t>31.10.2025</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>bob.smith</t>
+          <t>peter.brown</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Bob Smith</t>
+          <t>Peter Brown</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Operations Manager</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>24.06.2024</t>
+          <t>07.02.2025</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -3755,42 +3755,42 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>frank.miller</t>
+          <t>david.davis</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Frank Miller</t>
+          <t>David Davis</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Recruiter</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>05.08.2025</t>
+          <t>22.04.2024</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J25" s="9" t="inlineStr">
@@ -3807,27 +3807,27 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>carol.garcia</t>
+          <t>david.williams</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Carol Garcia</t>
+          <t>David Williams</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>IT Administrator</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>01.06.2024</t>
+          <t>01.07.2024</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>iris.garcia</t>
+          <t>mary.smith</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Iris Garcia</t>
+          <t>Mary Smith</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Recruiter</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>12.03.2024</t>
+          <t>12.08.2025</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -3911,17 +3911,17 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>kate.jones</t>
+          <t>kate.williams</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Kate Jones</t>
+          <t>Kate Williams</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>02.08.2024</t>
+          <t>13.08.2025</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>nathan.garcia</t>
+          <t>alice.johnson</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Nathan Garcia</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>29.08.2024</t>
+          <t>21.09.2025</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Operations Manager</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
@@ -4015,27 +4015,27 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>frank.brown</t>
+          <t>carol.jones</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Frank Brown</t>
+          <t>Carol Jones</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>24.05.2024</t>
+          <t>09.07.2025</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>Operations Manager</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
@@ -4067,27 +4067,27 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>bob.jones</t>
+          <t>kate.miller</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Bob Jones</t>
+          <t>Kate Miller</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>10.09.2024</t>
+          <t>30.07.2024</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
@@ -4119,32 +4119,32 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>liam.jones</t>
+          <t>iris.smith</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Liam Jones</t>
+          <t>Iris Smith</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>21.05.2025</t>
+          <t>01.06.2025</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>henry.johnson</t>
+          <t>peter.garcia</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Henry Johnson</t>
+          <t>Peter Garcia</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>23.06.2024</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
@@ -4223,27 +4223,27 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>peter.smith</t>
+          <t>nathan.smith</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Peter Smith</t>
+          <t>Nathan Smith</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Recruiter</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>28.10.2025</t>
+          <t>29.02.2024</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
@@ -4275,32 +4275,32 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>olivia.smith</t>
+          <t>david.williams</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Olivia Smith</t>
+          <t>David Williams</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>17.08.2025</t>
+          <t>19.07.2025</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>liam.miller</t>
+          <t>olivia.miller</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Liam Miller</t>
+          <t>Olivia Miller</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -4347,12 +4347,12 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>06.05.2024</t>
+          <t>06.09.2024</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
@@ -4379,32 +4379,32 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>jack.johnson</t>
+          <t>david.jones</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Jack Johnson</t>
+          <t>David Jones</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>13.08.2025</t>
+          <t>28.11.2024</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>carol.miller</t>
+          <t>olivia.brown</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Carol Miller</t>
+          <t>Olivia Brown</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Finance Analyst</t>
+          <t>IT Administrator</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>18.11.2024</t>
+          <t>16.07.2025</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
@@ -4483,27 +4483,27 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>jack.smith</t>
+          <t>peter.garcia</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Jack Smith</t>
+          <t>Peter Garcia</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>23.05.2025</t>
+          <t>14.08.2025</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
@@ -4535,17 +4535,17 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>jack.brown</t>
+          <t>carol.garcia</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Jack Brown</t>
+          <t>Carol Garcia</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -4555,22 +4555,22 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>05.02.2025</t>
+          <t>22.07.2024</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>Automatic</t>
-        </is>
-      </c>
-      <c r="H40" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Inherited</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="J40" s="9" t="inlineStr">
@@ -4587,32 +4587,32 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>david.garcia</t>
+          <t>carol.garcia</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>David Garcia</t>
+          <t>Carol Garcia</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>IT Administrator</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>23.02.2025</t>
+          <t>12.08.2025</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
@@ -4639,32 +4639,32 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>david.garcia</t>
+          <t>henry.williams</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>David Garcia</t>
+          <t>Henry Williams</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>18.06.2024</t>
+          <t>09.12.2025</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>mary.smith</t>
+          <t>henry.davis</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Mary Smith</t>
+          <t>Henry Davis</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>10.06.2024</t>
+          <t>18.03.2024</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="J43" s="9" t="inlineStr">
@@ -4743,42 +4743,42 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>nathan.miller</t>
+          <t>grace.jones</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Nathan Miller</t>
+          <t>Grace Jones</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Help Desk</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>19.03.2025</t>
+          <t>19.07.2025</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>Automatic</t>
-        </is>
-      </c>
-      <c r="H44" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>frank.miller</t>
+          <t>peter.davis</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Frank Miller</t>
+          <t>Peter Davis</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>27.04.2025</t>
+          <t>22.12.2025</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -4847,32 +4847,32 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>iris.johnson</t>
+          <t>emma.jones</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Iris Johnson</t>
+          <t>Emma Jones</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Sales Operations</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>24.01.2025</t>
+          <t>06.03.2025</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H46" s="9" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="J46" s="9" t="inlineStr">
@@ -4899,17 +4899,17 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>iris.williams</t>
+          <t>olivia.williams</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Iris Williams</t>
+          <t>Olivia Williams</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -4919,12 +4919,12 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>14.10.2024</t>
+          <t>03.12.2024</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H47" s="9" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="J47" s="9" t="inlineStr">
@@ -4951,27 +4951,27 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>alice.johnson</t>
+          <t>alice.garcia</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Alice Johnson</t>
+          <t>Alice Garcia</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>04.06.2025</t>
+          <t>10.01.2025</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="J48" s="9" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>alice.davis</t>
+          <t>david.miller</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Alice Davis</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>IT Administrator</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>14.09.2024</t>
+          <t>25.07.2024</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
@@ -5055,42 +5055,42 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>frank.miller</t>
+          <t>jack.smith</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Frank Miller</t>
+          <t>Jack Smith</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Recruiter</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>31.10.2025</t>
+          <t>28.04.2024</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
-        </is>
-      </c>
-      <c r="H50" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
         </is>
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J50" s="9" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>jack.johnson</t>
+          <t>mary.smith</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Jack Johnson</t>
+          <t>Mary Smith</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -5122,17 +5122,17 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>10.04.2024</t>
+          <t>04.01.2025</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
@@ -5159,32 +5159,32 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>mary.smith</t>
+          <t>frank.williams</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Mary Smith</t>
+          <t>Frank Williams</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>24.02.2024</t>
+          <t>12.01.2025</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="J52" s="9" t="inlineStr">
@@ -5211,27 +5211,27 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>henry.miller</t>
+          <t>kate.brown</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Henry Miller</t>
+          <t>Kate Brown</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>31.12.2025</t>
+          <t>23.06.2025</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="J53" s="9" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>mary.jones</t>
+          <t>mary.smith</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Mary Jones</t>
+          <t>Mary Smith</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -5278,17 +5278,17 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>06.03.2025</t>
+          <t>06.07.2025</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
@@ -5315,32 +5315,32 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>emma.johnson</t>
+          <t>nathan.williams</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Emma Johnson</t>
+          <t>Nathan Williams</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>11.06.2025</t>
+          <t>07.12.2024</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="J55" s="9" t="inlineStr">
@@ -5367,32 +5367,32 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>kate.davis</t>
+          <t>emma.williams</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Kate Davis</t>
+          <t>Emma Williams</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>11.05.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="J56" s="9" t="inlineStr">
@@ -5419,32 +5419,32 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>carol.davis</t>
+          <t>olivia.davis</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Carol Davis</t>
+          <t>Olivia Davis</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Marketing Specialist</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>07.07.2024</t>
+          <t>26.05.2024</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="J57" s="9" t="inlineStr">
@@ -5471,42 +5471,42 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>jack.smith</t>
+          <t>carol.davis</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Jack Smith</t>
+          <t>Carol Davis</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Finance Analyst</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>27.10.2025</t>
+          <t>04.02.2025</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
-        </is>
-      </c>
-      <c r="H58" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Automatic</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
         </is>
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="J58" s="9" t="inlineStr">
@@ -5523,27 +5523,27 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>nathan.jones</t>
+          <t>peter.williams</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Nathan Jones</t>
+          <t>Peter Williams</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>10.04.2025</t>
+          <t>26.05.2024</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J59" s="9" t="inlineStr">
@@ -5575,27 +5575,27 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>kate.brown</t>
+          <t>kate.garcia</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Kate Brown</t>
+          <t>Kate Garcia</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>Auditor</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>17.11.2025</t>
+          <t>24.06.2025</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
@@ -5603,14 +5603,14 @@
           <t>Automatic</t>
         </is>
       </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="J60" s="9" t="inlineStr">
@@ -5627,17 +5627,17 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>grace.miller</t>
+          <t>grace.garcia</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Grace Miller</t>
+          <t>Grace Garcia</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>14.10.2024</t>
+          <t>28.09.2024</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
@@ -5655,14 +5655,14 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J61" s="9" t="inlineStr">
@@ -5679,27 +5679,27 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>kate.miller</t>
+          <t>alice.miller</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Kate Miller</t>
+          <t>Alice Miller</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>04.08.2025</t>
+          <t>20.09.2025</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="J62" s="9" t="inlineStr">
@@ -5731,32 +5731,32 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>henry.brown</t>
+          <t>bob.jones</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Henry Brown</t>
+          <t>Bob Jones</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>21.10.2024</t>
+          <t>13.08.2024</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="H63" s="9" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J63" s="9" t="inlineStr">
@@ -5783,17 +5783,17 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>carol.smith</t>
+          <t>liam.brown</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Carol Smith</t>
+          <t>Liam Brown</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>18.04.2024</t>
+          <t>06.03.2025</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J64" s="9" t="inlineStr">
@@ -5835,27 +5835,27 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>iris.davis</t>
+          <t>david.garcia</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Iris Davis</t>
+          <t>David Garcia</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Operations Manager</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>23.05.2025</t>
+          <t>18.08.2025</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Operations Manager</t>
         </is>
       </c>
       <c r="J65" s="9" t="inlineStr">
@@ -5887,32 +5887,32 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>nathan.johnson</t>
+          <t>emma.brown</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Nathan Johnson</t>
+          <t>Emma Brown</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>19.05.2024</t>
+          <t>16.09.2024</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H66" s="9" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="J66" s="9" t="inlineStr">
@@ -5939,27 +5939,27 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>david.jones</t>
+          <t>jack.brown</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>David Jones</t>
+          <t>Jack Brown</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Marketing Specialist</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>06.03.2025</t>
+          <t>18.08.2025</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="J67" s="9" t="inlineStr">
@@ -5991,27 +5991,27 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>frank.williams</t>
+          <t>bob.jones</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Frank Williams</t>
+          <t>Bob Jones</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Recruiter</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>16.03.2024</t>
+          <t>06.11.2024</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="J68" s="9" t="inlineStr">
@@ -6043,32 +6043,32 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>henry.brown</t>
+          <t>alice.johnson</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>Henry Brown</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>19.09.2025</t>
+          <t>16.06.2024</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Inherited</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="J69" s="9" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>grace.miller</t>
+          <t>grace.williams</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Grace Miller</t>
+          <t>Grace Williams</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>15.09.2024</t>
+          <t>02.09.2025</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
@@ -6147,42 +6147,42 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>bob.davis</t>
+          <t>carol.miller</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Bob Davis</t>
+          <t>Carol Miller</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>08.12.2025</t>
+          <t>05.08.2025</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
-        </is>
-      </c>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
         </is>
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="J71" s="9" t="inlineStr">
@@ -6199,42 +6199,42 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>carol.brown</t>
+          <t>carol.miller</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Carol Brown</t>
+          <t>Carol Miller</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>02.06.2025</t>
+          <t>09.04.2025</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>Automatic</t>
-        </is>
-      </c>
-      <c r="H72" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Inherited</t>
+        </is>
+      </c>
+      <c r="H72" s="11" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="J72" s="9" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>kate.williams</t>
+          <t>bob.garcia</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>Kate Williams</t>
+          <t>Bob Garcia</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>HR Generalist</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>04.01.2026</t>
+          <t>25.09.2025</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
@@ -6303,32 +6303,32 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>alice.miller</t>
+          <t>iris.johnson</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Alice Miller</t>
+          <t>Iris Johnson</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>10.01.2025</t>
+          <t>26.04.2024</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="J74" s="9" t="inlineStr">
@@ -6355,27 +6355,27 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>alice.miller</t>
+          <t>david.brown</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>Alice Miller</t>
+          <t>David Brown</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>05.08.2025</t>
+          <t>11.04.2025</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="J75" s="9" t="inlineStr">
@@ -6407,32 +6407,32 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>liam.garcia</t>
+          <t>liam.jones</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Liam Garcia</t>
+          <t>Liam Jones</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>28.06.2025</t>
+          <t>17.12.2025</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H76" s="9" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="J76" s="9" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>henry.smith</t>
+          <t>emma.williams</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>Henry Smith</t>
+          <t>Emma Williams</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>06.06.2024</t>
+          <t>19.03.2024</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
@@ -6511,27 +6511,27 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>alice.garcia</t>
+          <t>david.williams</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Alice Garcia</t>
+          <t>David Williams</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>02.12.2025</t>
+          <t>03.11.2025</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="J78" s="9" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>david.davis</t>
+          <t>frank.jones</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Frank Jones</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>26.06.2025</t>
+          <t>27.01.2025</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
@@ -6615,27 +6615,27 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>henry.jones</t>
+          <t>henry.williams</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Henry Jones</t>
+          <t>Henry Williams</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>18.06.2025</t>
+          <t>16.04.2024</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="J80" s="9" t="inlineStr">
@@ -6667,27 +6667,27 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>david.smith</t>
+          <t>nathan.williams</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>David Smith</t>
+          <t>Nathan Williams</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>30.09.2025</t>
+          <t>23.04.2025</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="J81" s="9" t="inlineStr">
@@ -6719,32 +6719,32 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>nathan.johnson</t>
+          <t>kate.brown</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Nathan Johnson</t>
+          <t>Kate Brown</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>23.08.2025</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>Inherited</t>
+          <t>Automatic</t>
         </is>
       </c>
       <c r="H82" s="9" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>Operations Manager</t>
         </is>
       </c>
       <c r="J82" s="9" t="inlineStr">
@@ -6771,27 +6771,27 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>mary.brown</t>
+          <t>olivia.davis</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Mary Brown</t>
+          <t>Olivia Davis</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>19.02.2025</t>
+          <t>29.04.2025</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="J83" s="9" t="inlineStr">
@@ -6823,27 +6823,27 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>mary.jones</t>
+          <t>kate.miller</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Mary Jones</t>
+          <t>Kate Miller</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>01.09.2025</t>
+          <t>11.10.2024</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="J84" s="9" t="inlineStr">
@@ -6875,27 +6875,27 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>kate.jones</t>
+          <t>kate.johnson</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>Kate Jones</t>
+          <t>Kate Johnson</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Standard User</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>11.07.2025</t>
+          <t>20.04.2025</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="J85" s="9" t="inlineStr">
@@ -7029,47 +7029,47 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>nathan.davis</t>
+          <t>liam.williams</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Nathan Davis</t>
+          <t>Liam Williams</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>HR System</t>
+          <t>File Server</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>18.10.2023</t>
+          <t>05.06.2025</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Legacy access before RBAC implementation</t>
+          <t>Migration pending</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Create custom role for this access pattern</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>Migration Planned</t>
+          <t>Under review</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
         </is>
       </c>
     </row>
@@ -7081,22 +7081,22 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>jack.brown</t>
+          <t>carol.garcia</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Jack Brown</t>
+          <t>Carol Garcia</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>File Server</t>
+          <t>Finance System</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -7106,22 +7106,22 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>10.05.2023</t>
+          <t>23.10.2023</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Legacy access before RBAC implementation</t>
+          <t>Temporary project access</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>Review and remove access</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>Migration Planned</t>
+          <t>Under review</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
         </is>
       </c>
     </row>
@@ -7133,32 +7133,32 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>emma.williams</t>
+          <t>mary.davis</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Emma Williams</t>
+          <t>Mary Davis</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>File Server</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>18.08.2023</t>
+          <t>28.05.2024</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -7168,12 +7168,12 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Under review</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>Migration Planned</t>
+          <t>Review and remove access</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
         </is>
       </c>
     </row>
@@ -7185,37 +7185,37 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>david.brown</t>
+          <t>liam.garcia</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>David Brown</t>
+          <t>Liam Garcia</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>File Server</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>07.04.2025</t>
+          <t>07.10.2023</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>System limitation - role not supported</t>
+          <t>Migration pending</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -7223,9 +7223,9 @@
           <t>Migrate to role by Q2 2026</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>Migration Planned</t>
         </is>
       </c>
     </row>
@@ -7237,47 +7237,47 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>carol.jones</t>
+          <t>mary.garcia</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Carol Jones</t>
+          <t>Mary Garcia</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>HR System</t>
+          <t>Finance System</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>13.08.2023</t>
+          <t>03.07.2025</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Executive exception approved by CISO</t>
+          <t>System limitation - role not supported</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Review and remove access</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
+          <t>Under review</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>Migration Planned</t>
         </is>
       </c>
     </row>
@@ -7289,22 +7289,22 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>emma.brown</t>
+          <t>grace.miller</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Emma Brown</t>
+          <t>Grace Miller</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Database Server</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -7314,12 +7314,12 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>18.08.2024</t>
+          <t>29.01.2024</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Executive exception approved by CISO</t>
+          <t>System limitation - role not supported</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
@@ -7327,9 +7327,9 @@
           <t>Under review</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>Migration Planned</t>
         </is>
       </c>
     </row>
@@ -7341,47 +7341,47 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>bob.brown</t>
+          <t>carol.miller</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Bob Brown</t>
+          <t>Carol Miller</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>File Server</t>
+          <t>Database Server</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>18.09.2024</t>
+          <t>29.01.2025</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Executive exception approved by CISO</t>
+          <t>Migration pending</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Review and remove access</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>Migration Planned</t>
+          <t>Create custom role for this access pattern</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
         </is>
       </c>
     </row>
@@ -7393,12 +7393,12 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>bob.johnson</t>
+          <t>olivia.williams</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Bob Johnson</t>
+          <t>Olivia Williams</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -7408,17 +7408,17 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>HR System</t>
+          <t>File Server</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>04.04.2025</t>
+          <t>15.01.2024</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Under review</t>
+          <t>Migrate to role by Q2 2026</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
@@ -7445,22 +7445,22 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>mary.davis</t>
+          <t>mary.jones</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Mary Davis</t>
+          <t>Mary Jones</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>HR System</t>
+          <t>Finance System</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>16.06.2023</t>
+          <t>03.06.2023</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Migrate to role by Q2 2026</t>
+          <t>Create custom role for this access pattern</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>alice.davis</t>
+          <t>emma.brown</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Alice Davis</t>
+          <t>Emma Brown</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>HR System</t>
+          <t>Finance System</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -7522,17 +7522,17 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>17.07.2025</t>
+          <t>29.09.2024</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>Executive exception approved by CISO</t>
+          <t>Migration pending</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>Create custom role for this access pattern</t>
+          <t>Review and remove access</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
@@ -7549,37 +7549,37 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>nathan.garcia</t>
+          <t>peter.smith</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Nathan Garcia</t>
+          <t>Peter Smith</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Database Server</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>03.08.2025</t>
+          <t>25.01.2025</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>System limitation - role not supported</t>
+          <t>Migration pending</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
@@ -7587,9 +7587,9 @@
           <t>Migrate to role by Q2 2026</t>
         </is>
       </c>
-      <c r="J16" s="10" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>Migration Planned</t>
         </is>
       </c>
     </row>
@@ -7601,32 +7601,32 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>kate.jones</t>
+          <t>nathan.johnson</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Kate Jones</t>
+          <t>Nathan Johnson</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>16.06.2024</t>
+          <t>02.05.2024</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Review and remove access</t>
+          <t>Create custom role for this access pattern</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
@@ -7653,42 +7653,42 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>henry.garcia</t>
+          <t>iris.jones</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Henry Garcia</t>
+          <t>Iris Jones</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>Database Server</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>15.08.2024</t>
+          <t>15.04.2025</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Migration pending</t>
+          <t>Legacy access before RBAC implementation</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Review and remove access</t>
+          <t>Under review</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
@@ -7705,22 +7705,22 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>nathan.miller</t>
+          <t>bob.jones</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Nathan Miller</t>
+          <t>Bob Jones</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Finance System</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>23.04.2023</t>
+          <t>20.01.2025</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Executive exception approved by CISO</t>
+          <t>Migration pending</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
@@ -7743,9 +7743,9 @@
           <t>Under review</t>
         </is>
       </c>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>Migration Planned</t>
         </is>
       </c>
     </row>
@@ -7757,32 +7757,32 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>carol.williams</t>
+          <t>peter.smith</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Carol Williams</t>
+          <t>Peter Smith</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>25.06.2023</t>
+          <t>01.01.2024</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Under review</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
+          <t>Migrate to role by Q2 2026</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>Migration Planned</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>emma.brown</t>
+          <t>frank.jones</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Emma Brown</t>
+          <t>Frank Jones</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -7824,32 +7824,32 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>File Server</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>07.08.2025</t>
+          <t>22.07.2024</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>System limitation - role not supported</t>
+          <t>Migration pending</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Under review</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
+          <t>Review and remove access</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>Migration Planned</t>
         </is>
       </c>
     </row>
@@ -7861,32 +7861,32 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>peter.johnson</t>
+          <t>jack.smith</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Peter Johnson</t>
+          <t>Jack Smith</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Finance System</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Write</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>07.10.2023</t>
+          <t>26.06.2025</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -7913,47 +7913,47 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>peter.davis</t>
+          <t>carol.miller</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Peter Davis</t>
+          <t>Carol Miller</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Finance System</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>12.05.2023</t>
+          <t>20.11.2023</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Migration pending</t>
+          <t>Legacy access before RBAC implementation</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>Review and remove access</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
+          <t>Under review</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>Migration Planned</t>
         </is>
       </c>
     </row>
@@ -7965,47 +7965,47 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>nathan.williams</t>
+          <t>bob.johnson</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Nathan Williams</t>
+          <t>Bob Johnson</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Database Server</t>
+          <t>HR System</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>03.05.2024</t>
+          <t>13.04.2023</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Executive exception approved by CISO</t>
+          <t>Migration pending</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>Under review</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>Migration Planned</t>
+          <t>Review and remove access</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
         </is>
       </c>
     </row>
@@ -8017,47 +8017,47 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>emma.williams</t>
+          <t>alice.williams</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Emma Williams</t>
+          <t>Alice Williams</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>HR System</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Write</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>16.01.2025</t>
+          <t>08.03.2024</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>Executive exception approved by CISO</t>
+          <t>Legacy access before RBAC implementation</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Under review</t>
-        </is>
-      </c>
-      <c r="J25" s="11" t="inlineStr">
-        <is>
-          <t>Migration Planned</t>
+          <t>Migrate to role by Q2 2026</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
         </is>
       </c>
     </row>
@@ -8524,42 +8524,42 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>alice.miller</t>
+          <t>liam.brown</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>SOD-001</t>
+          <t>SOD-002</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>Sales Operations</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Finance Analyst</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>22.01.2026</t>
+          <t>05.02.2026</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Document exception with compensating controls</t>
+          <t>Remove Finance Analyst role from user</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="K6" s="10" t="inlineStr">
@@ -8581,22 +8581,22 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>peter.johnson</t>
+          <t>david.smith</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>SOD-001</t>
+          <t>SOD-003</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>IT Administrator</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Security Analyst</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -8606,22 +8606,22 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>06.02.2026</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>Document exception with compensating controls</t>
+          <t>Remove IT Administrator role from user</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>15.02.2026</t>
-        </is>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>01.03.2026</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>Remediation In Progress</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>david.williams</t>
+          <t>bob.jones</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>19.01.2026</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Remove Auditor role from user</t>
+          <t>Document exception with compensating controls</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="K8" s="10" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>peter.jones</t>
+          <t>henry.miller</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -8720,17 +8720,17 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>23.01.2026</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Reassign user to different department</t>
+          <t>Remove Security Analyst role from user</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>20.02.2026</t>
+          <t>06.03.2026</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>david.garcia</t>
+          <t>peter.williams</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -8777,22 +8777,22 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>02.02.2026</t>
+          <t>17.01.2026</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Remove Accounts Receivable role from user</t>
+          <t>Document exception with compensating controls</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>03.03.2026</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>Remediation In Progress</t>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
